--- a/reports/Performance_Load_Test_Report.xlsx
+++ b/reports/Performance_Load_Test_Report.xlsx
@@ -82,7 +82,7 @@
     <t>Successful Response Rate</t>
   </si>
   <si>
-    <t>99.85%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>&gt; 99.00%</t>
